--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BALONCESTO TALAVERA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BALONCESTO TALAVERA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. GACIC</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>34.02220000000001</v>
+        <v>31.9462</v>
       </c>
       <c r="E2" t="n">
-        <v>31.7152</v>
+        <v>24.4899</v>
       </c>
       <c r="F2" t="n">
-        <v>2.307</v>
+        <v>7.4564</v>
       </c>
       <c r="G2" t="n">
-        <v>25.1972</v>
+        <v>5.147199999999998</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.843400000000001</v>
+        <v>-4.3622</v>
       </c>
       <c r="I2" t="n">
-        <v>28.0403</v>
+        <v>9.509599999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>57.7547</v>
+        <v>43.3676</v>
       </c>
       <c r="K2" t="n">
-        <v>24.1521</v>
+        <v>23.2299</v>
       </c>
       <c r="L2" t="n">
-        <v>33.6028</v>
+        <v>20.1376</v>
       </c>
       <c r="M2" t="n">
-        <v>-32.5577</v>
+        <v>-38.2205</v>
       </c>
       <c r="N2" t="n">
-        <v>-26.9954</v>
+        <v>-27.592</v>
       </c>
       <c r="O2" t="n">
-        <v>-5.5623</v>
+        <v>-10.6287</v>
       </c>
       <c r="P2" t="n">
-        <v>-3.8807</v>
+        <v>9.701599999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-51.4186</v>
+        <v>-46.5678</v>
       </c>
       <c r="R2" t="n">
-        <v>47.538</v>
+        <v>56.2693</v>
       </c>
       <c r="S2" t="n">
-        <v>10.4809</v>
+        <v>-1.6516</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.5266</v>
+        <v>-4.9247</v>
       </c>
       <c r="U2" t="n">
-        <v>13.0075</v>
+        <v>3.2732</v>
       </c>
       <c r="V2" t="n">
-        <v>2.224899999999999</v>
+        <v>18.7491</v>
       </c>
       <c r="W2" t="n">
-        <v>27.9058</v>
+        <v>32.6146</v>
       </c>
       <c r="X2" t="n">
-        <v>-25.6808</v>
+        <v>-13.8657</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>S. GACIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>15.521</v>
+        <v>29.8807</v>
       </c>
       <c r="E3" t="n">
-        <v>18.2398</v>
+        <v>32.2838</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.718699999999999</v>
+        <v>-2.403499999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>8.071800000000001</v>
+        <v>25.1972</v>
       </c>
       <c r="H3" t="n">
-        <v>8.257</v>
+        <v>-2.843400000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1850999999999996</v>
+        <v>28.0403</v>
       </c>
       <c r="J3" t="n">
-        <v>27.5539</v>
+        <v>57.7547</v>
       </c>
       <c r="K3" t="n">
-        <v>19.1962</v>
+        <v>24.1521</v>
       </c>
       <c r="L3" t="n">
-        <v>8.357900000000001</v>
+        <v>33.6028</v>
       </c>
       <c r="M3" t="n">
-        <v>-19.4825</v>
+        <v>-32.5577</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.9398</v>
+        <v>-26.9954</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.5426</v>
+        <v>-5.5623</v>
       </c>
       <c r="P3" t="n">
-        <v>7.1791</v>
+        <v>-3.8807</v>
       </c>
       <c r="Q3" t="n">
-        <v>-25.0306</v>
+        <v>-51.4186</v>
       </c>
       <c r="R3" t="n">
-        <v>32.2092</v>
+        <v>47.538</v>
       </c>
       <c r="S3" t="n">
-        <v>14.5583</v>
+        <v>6.339099999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>10.7338</v>
+        <v>-1.958</v>
       </c>
       <c r="U3" t="n">
-        <v>3.8241</v>
+        <v>8.2972</v>
       </c>
       <c r="V3" t="n">
-        <v>-14.2879</v>
+        <v>2.224899999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>4.9821</v>
+        <v>27.9058</v>
       </c>
       <c r="X3" t="n">
-        <v>-19.2698</v>
+        <v>-25.6808</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>11.6199</v>
+        <v>6.7746</v>
       </c>
       <c r="E4" t="n">
-        <v>11.1461</v>
+        <v>5.843400000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4734999999999999</v>
+        <v>0.9311999999999998</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3163000000000011</v>
@@ -766,13 +766,13 @@
         <v>14.9404</v>
       </c>
       <c r="S4" t="n">
-        <v>10.5982</v>
+        <v>5.7528</v>
       </c>
       <c r="T4" t="n">
-        <v>9.4411</v>
+        <v>4.1383</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1573</v>
+        <v>1.6147</v>
       </c>
       <c r="V4" t="n">
         <v>-2.3487</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>11.4417</v>
+        <v>6.702200000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>20.9208</v>
+        <v>10.3979</v>
       </c>
       <c r="F5" t="n">
-        <v>-9.4793</v>
+        <v>-3.695199999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.436199999999998</v>
+        <v>8.071800000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3748999999999993</v>
+        <v>8.257</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0613</v>
+        <v>-0.1850999999999996</v>
       </c>
       <c r="J5" t="n">
-        <v>38.9706</v>
+        <v>27.5539</v>
       </c>
       <c r="K5" t="n">
-        <v>27.8267</v>
+        <v>19.1962</v>
       </c>
       <c r="L5" t="n">
-        <v>11.1438</v>
+        <v>8.357900000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-36.5342</v>
+        <v>-19.4825</v>
       </c>
       <c r="N5" t="n">
-        <v>-27.452</v>
+        <v>-10.9398</v>
       </c>
       <c r="O5" t="n">
-        <v>-9.082000000000001</v>
+        <v>-8.5426</v>
       </c>
       <c r="P5" t="n">
-        <v>-8.9255</v>
+        <v>7.1791</v>
       </c>
       <c r="Q5" t="n">
-        <v>-56.2693</v>
+        <v>-25.0306</v>
       </c>
       <c r="R5" t="n">
-        <v>47.3439</v>
+        <v>32.2092</v>
       </c>
       <c r="S5" t="n">
-        <v>34.2509</v>
+        <v>5.7392</v>
       </c>
       <c r="T5" t="n">
-        <v>24.0681</v>
+        <v>2.8916</v>
       </c>
       <c r="U5" t="n">
-        <v>10.1833</v>
+        <v>2.8478</v>
       </c>
       <c r="V5" t="n">
-        <v>-16.3203</v>
+        <v>-14.2879</v>
       </c>
       <c r="W5" t="n">
-        <v>14.1518</v>
+        <v>4.9821</v>
       </c>
       <c r="X5" t="n">
-        <v>-30.4723</v>
+        <v>-19.2698</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>F. REJON MIGUEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>11.0206</v>
+        <v>-2.3242</v>
       </c>
       <c r="E6" t="n">
-        <v>7.905500000000002</v>
+        <v>-1.3563</v>
       </c>
       <c r="F6" t="n">
-        <v>3.115</v>
+        <v>-0.9679</v>
       </c>
       <c r="G6" t="n">
-        <v>5.147199999999998</v>
+        <v>-2.0388</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.3622</v>
+        <v>-1.0884</v>
       </c>
       <c r="I6" t="n">
-        <v>9.509599999999999</v>
+        <v>-0.9504000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>43.3676</v>
+        <v>-0.7085</v>
       </c>
       <c r="K6" t="n">
-        <v>23.2299</v>
+        <v>-0.9927</v>
       </c>
       <c r="L6" t="n">
-        <v>20.1376</v>
+        <v>0.2842</v>
       </c>
       <c r="M6" t="n">
-        <v>-38.2205</v>
+        <v>-1.3302</v>
       </c>
       <c r="N6" t="n">
-        <v>-27.592</v>
+        <v>-0.0955</v>
       </c>
       <c r="O6" t="n">
-        <v>-10.6287</v>
+        <v>-1.2346</v>
       </c>
       <c r="P6" t="n">
-        <v>9.701599999999999</v>
+        <v>0.9701000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-46.5678</v>
+        <v>-0.3881</v>
       </c>
       <c r="R6" t="n">
-        <v>56.2693</v>
+        <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>-22.5771</v>
+        <v>-0.4094</v>
       </c>
       <c r="T6" t="n">
-        <v>-21.5095</v>
+        <v>-0.2596000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0681</v>
+        <v>-0.1497</v>
       </c>
       <c r="V6" t="n">
-        <v>18.7491</v>
+        <v>-0.8462</v>
       </c>
       <c r="W6" t="n">
-        <v>32.6146</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.8657</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>A. PASTOR LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.035399999999999</v>
+        <v>-4.4917</v>
       </c>
       <c r="E7" t="n">
-        <v>8.431999999999999</v>
+        <v>-1.908</v>
       </c>
       <c r="F7" t="n">
-        <v>-10.4675</v>
+        <v>-2.5838</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.0125</v>
+        <v>-2.5559</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9328000000000003</v>
+        <v>-2.5853</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.0802</v>
+        <v>0.02940000000000003</v>
       </c>
       <c r="J7" t="n">
-        <v>9.5654</v>
+        <v>-1.7965</v>
       </c>
       <c r="K7" t="n">
-        <v>3.394699999999999</v>
+        <v>-1.1698</v>
       </c>
       <c r="L7" t="n">
-        <v>6.1706</v>
+        <v>-0.6267</v>
       </c>
       <c r="M7" t="n">
-        <v>-15.578</v>
+        <v>-0.7592</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.3272</v>
+        <v>-1.4153</v>
       </c>
       <c r="O7" t="n">
-        <v>-11.2505</v>
+        <v>0.6561</v>
       </c>
       <c r="P7" t="n">
-        <v>-26.9704</v>
+        <v>1.1642</v>
       </c>
       <c r="Q7" t="n">
-        <v>-45.9859</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>19.0152</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>15.3108</v>
+        <v>-0.9917</v>
       </c>
       <c r="T7" t="n">
-        <v>15.4884</v>
+        <v>-0.1113</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1778000000000001</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>15.6368</v>
+        <v>-2.1083</v>
       </c>
       <c r="W7" t="n">
-        <v>29.3639</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-13.727</v>
+        <v>-2.1083</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. REJON MIGUEL</t>
+          <t>R. MARQUINA ROMERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3336</v>
+        <v>-5.398400000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5565</v>
+        <v>-2.3827</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7771</v>
+        <v>-3.0156</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0388</v>
+        <v>-4.7793</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0884</v>
+        <v>-1.9081</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9504000000000001</v>
+        <v>-2.8713</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7085</v>
+        <v>0.2127999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9927</v>
+        <v>-0.4696</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2842</v>
+        <v>0.6824999999999998</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3302</v>
+        <v>-4.9923</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0955</v>
+        <v>-1.4383</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2346</v>
+        <v>-3.5536</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9701000000000001</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.3881</v>
+        <v>-3.1046</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3582</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4188</v>
+        <v>0.4792000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4598</v>
+        <v>0.509</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0411</v>
+        <v>-0.02969999999999998</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8462</v>
+        <v>0.066</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8462</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PASTOR LOPEZ</t>
+          <t>I. GARCIA BENITO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.0646</v>
+        <v>-6.1396</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2083</v>
+        <v>-3.4845</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8563</v>
+        <v>-2.6554</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5559</v>
+        <v>-2.9598</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5853</v>
+        <v>1.811</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02940000000000003</v>
+        <v>-4.7708</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7965</v>
+        <v>0.8340999999999998</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1698</v>
+        <v>0.5274</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6267</v>
+        <v>0.3066999999999995</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7592</v>
+        <v>-3.7939</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4153</v>
+        <v>1.2835</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6561</v>
+        <v>-5.0774</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1642</v>
+        <v>0.1939999999999997</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-6.9851</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1642</v>
+        <v>7.1791</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5646</v>
+        <v>-0.4486</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4116</v>
+        <v>0.8308</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1529</v>
+        <v>-1.2796</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1083</v>
+        <v>-2.925</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8358</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1083</v>
+        <v>-4.760899999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. MARQUINA ROMERO</t>
+          <t>D. LORENZO  NEGRETE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.8349</v>
+        <v>-6.335200000000003</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6831</v>
+        <v>10.6579</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1518</v>
+        <v>-16.9936</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.7793</v>
+        <v>-6.9927</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9081</v>
+        <v>-11.7122</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8713</v>
+        <v>4.719400000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2127999999999999</v>
+        <v>35.7048</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4696</v>
+        <v>13.1163</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6824999999999998</v>
+        <v>22.5886</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.9923</v>
+        <v>-42.6976</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4383</v>
+        <v>-24.8286</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.5536</v>
+        <v>-17.8689</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1642</v>
+        <v>-21.5375</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1046</v>
+        <v>-66.55319999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9403</v>
+        <v>45.0154</v>
       </c>
       <c r="S10" t="n">
-        <v>0.04250000000000004</v>
+        <v>3.5187</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2087</v>
+        <v>-0.9905000000000003</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1659</v>
+        <v>4.508800000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.066</v>
+        <v>18.6764</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>42.4965</v>
       </c>
       <c r="X10" t="n">
-        <v>0.066</v>
+        <v>-23.8203</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. GARCIA BENITO</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.4864</v>
+        <v>-8.0639</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.6075</v>
+        <v>4.209199999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8788</v>
+        <v>-12.2735</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9598</v>
+        <v>2.436199999999998</v>
       </c>
       <c r="H11" t="n">
-        <v>1.811</v>
+        <v>0.3748999999999993</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.7708</v>
+        <v>2.0613</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8340999999999998</v>
+        <v>38.9706</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5274</v>
+        <v>27.8267</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3066999999999995</v>
+        <v>11.1438</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.7939</v>
+        <v>-36.5342</v>
       </c>
       <c r="N11" t="n">
-        <v>1.2835</v>
+        <v>-27.452</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.0774</v>
+        <v>-9.082000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1939999999999997</v>
+        <v>-8.9255</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.9851</v>
+        <v>-56.2693</v>
       </c>
       <c r="R11" t="n">
-        <v>7.1791</v>
+        <v>47.3439</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.7956</v>
+        <v>14.7456</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2922</v>
+        <v>7.3566</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.5034</v>
+        <v>7.388999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.925</v>
+        <v>-16.3203</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8358</v>
+        <v>14.1518</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.760899999999999</v>
+        <v>-30.4723</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. BALDAN MARTÍN</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.0283</v>
+        <v>-11.9416</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.3936</v>
+        <v>-1.2119</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.6349</v>
+        <v>-10.7295</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.3081</v>
+        <v>-6.0125</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3327999999999999</v>
+        <v>-0.9328000000000003</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.9752</v>
+        <v>-5.0802</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2129999999999997</v>
+        <v>9.5654</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0382</v>
+        <v>3.394699999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.251</v>
+        <v>6.1706</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.095</v>
+        <v>-15.578</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3709</v>
+        <v>-4.3272</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.724</v>
+        <v>-11.2505</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.821</v>
+        <v>-26.9704</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.1945</v>
+        <v>-45.9859</v>
       </c>
       <c r="R12" t="n">
-        <v>7.3732</v>
+        <v>19.0152</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7283000000000001</v>
+        <v>5.4047</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5025000000000001</v>
+        <v>5.8443</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2255999999999999</v>
+        <v>-0.4399000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-8.1714</v>
+        <v>15.6368</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5164000000000001</v>
+        <v>29.3639</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.687800000000001</v>
+        <v>-13.727</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. LORENZO  NEGRETE</t>
+          <t>M. BALDAN MARTÍN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.0549</v>
+        <v>-17.0706</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5607000000000006</v>
+        <v>-12.8116</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.4946</v>
+        <v>-4.2592</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.9927</v>
+        <v>-3.3081</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.7122</v>
+        <v>-0.3327999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>4.719400000000001</v>
+        <v>-2.9752</v>
       </c>
       <c r="J13" t="n">
-        <v>35.7048</v>
+        <v>-0.2129999999999997</v>
       </c>
       <c r="K13" t="n">
-        <v>13.1163</v>
+        <v>1.0382</v>
       </c>
       <c r="L13" t="n">
-        <v>22.5886</v>
+        <v>-1.251</v>
       </c>
       <c r="M13" t="n">
-        <v>-42.6976</v>
+        <v>-3.095</v>
       </c>
       <c r="N13" t="n">
-        <v>-24.8286</v>
+        <v>-1.3709</v>
       </c>
       <c r="O13" t="n">
-        <v>-17.8689</v>
+        <v>-1.724</v>
       </c>
       <c r="P13" t="n">
-        <v>-21.5375</v>
+        <v>-5.821</v>
       </c>
       <c r="Q13" t="n">
-        <v>-66.55319999999999</v>
+        <v>-13.1945</v>
       </c>
       <c r="R13" t="n">
-        <v>45.0154</v>
+        <v>7.3732</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.201000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="T13" t="n">
-        <v>-12.2091</v>
+        <v>0.07949999999999996</v>
       </c>
       <c r="U13" t="n">
-        <v>3.008</v>
+        <v>0.1505000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>18.6764</v>
+        <v>-8.1714</v>
       </c>
       <c r="W13" t="n">
-        <v>42.4965</v>
+        <v>0.5164000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-23.8203</v>
+        <v>-8.687800000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-32.9806</v>
+        <v>-19.6325</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.4714</v>
+        <v>-1.718300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-22.509</v>
+        <v>-17.9145</v>
       </c>
       <c r="G14" t="n">
         <v>-1.861800000000001</v>
@@ -1546,13 +1546,13 @@
         <v>47.1499</v>
       </c>
       <c r="S14" t="n">
-        <v>-19.4933</v>
+        <v>-6.1451</v>
       </c>
       <c r="T14" t="n">
-        <v>-14.496</v>
+        <v>-5.742599999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.9975</v>
+        <v>-0.4025000000000002</v>
       </c>
       <c r="V14" t="n">
         <v>-5.0283</v>
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-35.2458</v>
+        <v>-26.0403</v>
       </c>
       <c r="E15" t="n">
-        <v>-31.302</v>
+        <v>-25.4678</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.9438</v>
+        <v>-0.5726000000000009</v>
       </c>
       <c r="G15" t="n">
         <v>-22.7309</v>
@@ -1624,13 +1624,13 @@
         <v>39.1947</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.2394</v>
+        <v>0.9661</v>
       </c>
       <c r="T15" t="n">
-        <v>-8.793699999999999</v>
+        <v>-2.9593</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5546</v>
+        <v>3.9256</v>
       </c>
       <c r="V15" t="n">
         <v>-4.8573</v>
@@ -1657,22 +1657,22 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-46.4391</v>
+        <v>-32.13430000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>30.57630000000001</v>
+        <v>37.54100000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-77.01629999999999</v>
+        <v>-69.6767</v>
       </c>
       <c r="G16" t="n">
-        <v>-12.70370000000001</v>
+        <v>-12.7037</v>
       </c>
       <c r="H16" t="n">
         <v>-35.7561</v>
       </c>
       <c r="I16" t="n">
-        <v>23.05139999999999</v>
+        <v>23.0514</v>
       </c>
       <c r="J16" t="n">
         <v>251.4006</v>
@@ -1702,16 +1702,16 @@
         <v>367.691</v>
       </c>
       <c r="S16" t="n">
-        <v>19.22349999999999</v>
+        <v>33.529</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.260899999999996</v>
+        <v>4.7041</v>
       </c>
       <c r="U16" t="n">
-        <v>21.4847</v>
+        <v>28.8249</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.540200000000006</v>
+        <v>-1.540200000000004</v>
       </c>
       <c r="W16" t="n">
         <v>200.5471</v>
